--- a/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65084_completo.xlsx
+++ b/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65084_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R61d865704f2d44cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R99e5069fe7b144ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,486 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    885.0032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    893.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.9324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.8055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    957.0392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    985.3915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    995.0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1004.6986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1044.2865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1085.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1024.3303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    966.4088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    902.5254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    911.4082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    957.0392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    995.0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    885.0032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    911.4082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    885.0032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    763.9312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    786.6852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    786.6852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65084_completo.xlsx
+++ b/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65084_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R99e5069fe7b144ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2271e8dcbf4b4de7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2856 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    966.4088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1014.4739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1064.5673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1357.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1839.0296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.4172</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    794.4321</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    734.7284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    741.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    741.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    749.1675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    749.1675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    763.9312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    771.4347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    786.6852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    826.2312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.6175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.4172</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    975.8596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    975.8596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    985.3915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1054.3863</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1085.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1116.6890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1138.1057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1333.2503</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1357.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1420.4192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1382.5743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.3568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1170.8392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1193.0671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1170.8392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    802.2602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    818.1597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    834.3838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.9324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1024.3303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1044.2865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1064.5673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1085.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.3568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1148.9357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1181.9126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1193.0671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1138.1057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1074.8294</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    938.5434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.6175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.8055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    893.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    920.3721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    902.5254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    938.5434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    975.8596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    947.7507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.4172</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    920.3721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.4172</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    975.8596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1004.6986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1024.3303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    975.8596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.9324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    885.0032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    902.5254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    966.4088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    995.0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1034.2678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1074.8294</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1170.8392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1238.4967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1273.4208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1309.0751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1749.4658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1823.8995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1662.8229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1485.1167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1159.8469</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1138.1057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.3568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1148.9357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1148.9357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1170.8392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1238.4967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1285.2244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.3568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1170.8392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1193.0671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1215.6196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1648.6664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1720.2603</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1915.8972</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2075.7175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1551.8426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    741.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    727.6306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    727.6306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    734.7284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    734.7284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    741.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    749.1675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    763.9312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    794.4321</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    818.1597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    826.2312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.9324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    902.5254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    947.7507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.6175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    885.0032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    794.4321</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    826.2312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    680.2173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    673.7685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    673.7685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    680.2173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    686.7472</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    686.7472</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    693.3583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    693.3583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    706.8238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    706.8238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    713.6783</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    720.6139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    727.6306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    727.6306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    734.7284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    734.7284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    741.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    749.1675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    763.9312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    706.8238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    713.6783</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    727.6306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    749.1675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    771.4347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    771.4347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.5088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    763.9312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    771.4347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    779.0194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    826.2312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.9324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.8055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.3284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    893.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    947.7507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    985.3915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1014.4739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1044.2865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1085.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.3568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1333.2503</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1357.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1420.4192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1458.9943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1884.9067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1839.0296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1648.6664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1551.8426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1297.1092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1238.4967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1116.6890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1044.2865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1074.8294</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    995.0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    920.3721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
